--- a/ig/homecareobservation/StructureDefinition-medcom-homecareobservation-messageheader.xlsx
+++ b/ig/homecareobservation/StructureDefinition-medcom-homecareobservation-messageheader.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T07:53:40+00:00</t>
+    <t>2026-06-03T08:12:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1977,7 +1977,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>254</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>295</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>296</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>303</v>
       </c>
@@ -8857,7 +8857,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>319</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>320</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>323</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>342</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>374</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>435</v>
       </c>
@@ -11650,12 +11650,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM89">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
